--- a/exports/trend_1d/IEX_full_report.xlsx
+++ b/exports/trend_1d/IEX_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43152</v>
+        <v>43153</v>
       </c>
       <c r="H2" t="n">
-        <v>50.35</v>
+        <v>49.65</v>
       </c>
       <c r="I2" t="n">
         <v>50.26618041811636</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.71</v>
+        <v>-7.02</v>
       </c>
       <c r="L2" t="n">
-        <v>7.02</v>
+        <v>7.21</v>
       </c>
       <c r="M2" t="n">
         <v>4.08</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.85</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43185</v>
+        <v>43186</v>
       </c>
       <c r="H3" t="n">
-        <v>50.55</v>
+        <v>51.45</v>
       </c>
       <c r="I3" t="n">
         <v>50.88689185801321</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.81</v>
+        <v>-3.63</v>
       </c>
       <c r="L3" t="n">
         <v>6.65</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.57</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H4" t="n">
-        <v>52.75</v>
+        <v>51.65</v>
       </c>
       <c r="I4" t="n">
         <v>51.9841485259124</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" t="n">
-        <v>2.53</v>
+        <v>0.39</v>
       </c>
       <c r="L4" t="n">
         <v>2.82</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.48</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43336</v>
+        <v>43339</v>
       </c>
       <c r="H5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I5" t="n">
         <v>55.80743106490021</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.49</v>
+        <v>-10.36</v>
       </c>
       <c r="L5" t="n">
-        <v>9.68</v>
+        <v>13.17</v>
       </c>
       <c r="M5" t="n">
         <v>2.44</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.2</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43374</v>
+        <v>43376</v>
       </c>
       <c r="H6" t="n">
-        <v>53.65</v>
+        <v>53.4</v>
       </c>
       <c r="I6" t="n">
         <v>53.53596158856513</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.88</v>
+        <v>-6.32</v>
       </c>
       <c r="L6" t="n">
         <v>8.77</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.12</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43755</v>
+        <v>43756</v>
       </c>
       <c r="H7" t="n">
-        <v>45.15</v>
+        <v>48.9</v>
       </c>
       <c r="I7" t="n">
         <v>45.89674631668534</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K7" t="n">
-        <v>15.45</v>
+        <v>8.43</v>
       </c>
       <c r="L7" t="n">
         <v>9.74</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>254</v>
+        <v>255</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>13</v>
+      </c>
+      <c r="U7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>22.33</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H8" t="n">
-        <v>55.55</v>
+        <v>53.7</v>
       </c>
       <c r="I8" t="n">
         <v>53.93049244788868</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K8" t="n">
-        <v>13.6</v>
+        <v>9.82</v>
       </c>
       <c r="L8" t="n">
         <v>10.94</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>17.57</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43871</v>
+        <v>43872</v>
       </c>
       <c r="H9" t="n">
-        <v>60.95</v>
+        <v>62.95</v>
       </c>
       <c r="I9" t="n">
         <v>61.47734492557053</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>-13.5</v>
+        <v>-17.23</v>
       </c>
       <c r="L9" t="n">
-        <v>14.8</v>
+        <v>18.25</v>
       </c>
       <c r="M9" t="n">
         <v>1.51</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>15.9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H10" t="n">
-        <v>56.65</v>
+        <v>49.95</v>
       </c>
       <c r="I10" t="n">
         <v>55.41897335765682</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.01</v>
+        <v>-20.65</v>
       </c>
       <c r="L10" t="n">
-        <v>13.58</v>
+        <v>22.88</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>9.44</v>
       </c>
       <c r="N10" t="n">
-        <v>7.04</v>
+        <v>11.83</v>
       </c>
       <c r="O10" t="n">
         <v>3.28</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>28.11</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H11" t="n">
-        <v>54.6</v>
+        <v>57.7</v>
       </c>
       <c r="I11" t="n">
         <v>54.97098652413448</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.31</v>
+        <v>-15.52</v>
       </c>
       <c r="L11" t="n">
-        <v>18.12</v>
+        <v>18.42</v>
       </c>
       <c r="M11" t="n">
         <v>6</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>14.45</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44138</v>
+        <v>44139</v>
       </c>
       <c r="H12" t="n">
-        <v>62</v>
+        <v>60.4</v>
       </c>
       <c r="I12" t="n">
         <v>61.87315237923793</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K12" t="n">
-        <v>7.45</v>
+        <v>4.68</v>
       </c>
       <c r="L12" t="n">
         <v>6.24</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>12.57</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44145</v>
+        <v>44146</v>
       </c>
       <c r="H13" t="n">
-        <v>67.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>67.99051545857543</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>-11.26</v>
+        <v>-12.75</v>
       </c>
       <c r="L13" t="n">
-        <v>13</v>
+        <v>14.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.32</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.53</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44342</v>
+        <v>44343</v>
       </c>
       <c r="H14" t="n">
-        <v>118.8</v>
+        <v>117.55</v>
       </c>
       <c r="I14" t="n">
         <v>118.5180416380487</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K14" t="n">
-        <v>74.45</v>
+        <v>72.61</v>
       </c>
       <c r="L14" t="n">
         <v>2.28</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>11.56</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44382</v>
+        <v>44383</v>
       </c>
       <c r="H15" t="n">
-        <v>130.2</v>
+        <v>130.95</v>
       </c>
       <c r="I15" t="n">
         <v>130.778329808364</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.76</v>
+        <v>-11.4</v>
       </c>
       <c r="L15" t="n">
-        <v>12.34</v>
+        <v>14.04</v>
       </c>
       <c r="M15" t="n">
         <v>1.13</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.32</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H16" t="n">
-        <v>254.85</v>
+        <v>233</v>
       </c>
       <c r="I16" t="n">
         <v>243.5844251817128</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K16" t="n">
-        <v>94.62</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>1.99</v>
@@ -1353,7 +1544,7 @@
         <v>1.83</v>
       </c>
       <c r="N16" t="n">
-        <v>6.62</v>
+        <v>8.57</v>
       </c>
       <c r="O16" t="n">
         <v>0.58</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>29.67</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44539</v>
+        <v>44540</v>
       </c>
       <c r="H17" t="n">
-        <v>269.85</v>
+        <v>295.25</v>
       </c>
       <c r="I17" t="n">
         <v>274.8549514321553</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K17" t="n">
-        <v>-15.82</v>
+        <v>-26.72</v>
       </c>
       <c r="L17" t="n">
-        <v>20.02</v>
+        <v>30.39</v>
       </c>
       <c r="M17" t="n">
         <v>1.79</v>
       </c>
       <c r="N17" t="n">
-        <v>5.84</v>
+        <v>9.41</v>
       </c>
       <c r="O17" t="n">
         <v>-8.57</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>17.61</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H18" t="n">
-        <v>256.1</v>
+        <v>238.6</v>
       </c>
       <c r="I18" t="n">
         <v>245.0297123678496</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.26</v>
+        <v>-19.19</v>
       </c>
       <c r="L18" t="n">
-        <v>13.63</v>
+        <v>20.27</v>
       </c>
       <c r="M18" t="n">
-        <v>1.39</v>
+        <v>2.38</v>
       </c>
       <c r="N18" t="n">
-        <v>6.22</v>
+        <v>6.83</v>
       </c>
       <c r="O18" t="n">
         <v>9.41</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>20.79</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44630</v>
+        <v>44631</v>
       </c>
       <c r="H19" t="n">
-        <v>224.55</v>
+        <v>225.15</v>
       </c>
       <c r="I19" t="n">
         <v>224.572136605814</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K19" t="n">
-        <v>5.89</v>
+        <v>5.64</v>
       </c>
       <c r="L19" t="n">
         <v>14</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>12.21</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H20" t="n">
-        <v>230.2</v>
+        <v>218.5</v>
       </c>
       <c r="I20" t="n">
         <v>223.3659956973099</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K20" t="n">
-        <v>2.24</v>
+        <v>-2.95</v>
       </c>
       <c r="L20" t="n">
         <v>3.8</v>
       </c>
       <c r="M20" t="n">
-        <v>1.36</v>
+        <v>2.48</v>
       </c>
       <c r="N20" t="n">
-        <v>3.09</v>
+        <v>5.08</v>
       </c>
       <c r="O20" t="n">
         <v>0.27</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.93</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44785</v>
+        <v>44789</v>
       </c>
       <c r="H21" t="n">
-        <v>165.15</v>
+        <v>171.85</v>
       </c>
       <c r="I21" t="n">
         <v>167.4803654756565</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K21" t="n">
-        <v>24.42</v>
+        <v>21.35</v>
       </c>
       <c r="L21" t="n">
         <v>5.26</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>10.34</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44792</v>
+        <v>44795</v>
       </c>
       <c r="H22" t="n">
-        <v>163.75</v>
+        <v>157.1</v>
       </c>
       <c r="I22" t="n">
         <v>159.4610033603399</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.71</v>
+        <v>-8.58</v>
       </c>
       <c r="L22" t="n">
-        <v>5.44</v>
+        <v>8.93</v>
       </c>
       <c r="M22" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>4.06</v>
       </c>
       <c r="O22" t="n">
         <v>4.06</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>12.83</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44889</v>
+        <v>44890</v>
       </c>
       <c r="H23" t="n">
-        <v>146.95</v>
+        <v>150.35</v>
       </c>
       <c r="I23" t="n">
         <v>147.3305323302938</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K23" t="n">
-        <v>6.46</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>5.32</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>9.83</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H24" t="n">
-        <v>141.1</v>
+        <v>138.4</v>
       </c>
       <c r="I24" t="n">
         <v>140.3708274010547</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.15</v>
+        <v>-7.95</v>
       </c>
       <c r="L24" t="n">
-        <v>6.62</v>
+        <v>8.48</v>
       </c>
       <c r="M24" t="n">
         <v>0.38</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.77</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44977</v>
+        <v>44978</v>
       </c>
       <c r="H25" t="n">
-        <v>138.25</v>
+        <v>144.05</v>
       </c>
       <c r="I25" t="n">
         <v>142.9729252950319</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K25" t="n">
-        <v>0.11</v>
+        <v>-4.08</v>
       </c>
       <c r="L25" t="n">
-        <v>3.9</v>
+        <v>5.24</v>
       </c>
       <c r="M25" t="n">
         <v>2.26</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>8.69</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45009</v>
+        <v>45012</v>
       </c>
       <c r="H26" t="n">
-        <v>142.95</v>
+        <v>134.15</v>
       </c>
       <c r="I26" t="n">
         <v>139.1649901818999</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.76</v>
+        <v>-6.87</v>
       </c>
       <c r="L26" t="n">
-        <v>4.06</v>
+        <v>7.32</v>
       </c>
       <c r="M26" t="n">
         <v>1.79</v>
       </c>
       <c r="N26" t="n">
-        <v>3.83</v>
+        <v>6.16</v>
       </c>
       <c r="O26" t="n">
         <v>4.2</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>13.51</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H27" t="n">
-        <v>136.5</v>
+        <v>150.85</v>
       </c>
       <c r="I27" t="n">
         <v>142.7852972367202</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.75</v>
+        <v>-12.45</v>
       </c>
       <c r="L27" t="n">
-        <v>6.6</v>
+        <v>13.23</v>
       </c>
       <c r="M27" t="n">
         <v>1.33</v>
       </c>
       <c r="N27" t="n">
-        <v>4.61</v>
+        <v>10.51</v>
       </c>
       <c r="O27" t="n">
         <v>-6.16</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>16.17</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="H28" t="n">
-        <v>153.2</v>
+        <v>147.2</v>
       </c>
       <c r="I28" t="n">
         <v>151.5634330804049</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K28" t="n">
-        <v>1.56</v>
+        <v>-2.42</v>
       </c>
       <c r="L28" t="n">
         <v>9.35</v>
@@ -2037,7 +2372,7 @@
         <v>0.42</v>
       </c>
       <c r="N28" t="n">
-        <v>2.68</v>
+        <v>3.92</v>
       </c>
       <c r="O28" t="n">
         <v>10.51</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.01</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45146</v>
+        <v>45147</v>
       </c>
       <c r="H29" t="n">
-        <v>129.05</v>
+        <v>130.6</v>
       </c>
       <c r="I29" t="n">
         <v>130.5580829194129</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K29" t="n">
-        <v>12.33</v>
+        <v>11.28</v>
       </c>
       <c r="L29" t="n">
         <v>4.45</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="H30" t="n">
-        <v>133</v>
+        <v>129.65</v>
       </c>
       <c r="I30" t="n">
         <v>129.8265892966822</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K30" t="n">
-        <v>1.84</v>
+        <v>-0.73</v>
       </c>
       <c r="L30" t="n">
         <v>6.7</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.52</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="H31" t="n">
-        <v>127.6</v>
+        <v>133.45</v>
       </c>
       <c r="I31" t="n">
         <v>133.4061103654004</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K31" t="n">
-        <v>1.58</v>
+        <v>-2.93</v>
       </c>
       <c r="L31" t="n">
         <v>5.75</v>
@@ -2208,7 +2579,7 @@
         <v>2.01</v>
       </c>
       <c r="N31" t="n">
-        <v>2.74</v>
+        <v>4.58</v>
       </c>
       <c r="O31" t="n">
         <v>-2.52</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H32" t="n">
-        <v>164.1</v>
+        <v>147.25</v>
       </c>
       <c r="I32" t="n">
         <v>149.7496158467736</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K32" t="n">
-        <v>22.97</v>
+        <v>10.34</v>
       </c>
       <c r="L32" t="n">
         <v>4.23</v>
       </c>
       <c r="M32" t="n">
-        <v>1.25</v>
+        <v>5.42</v>
       </c>
       <c r="N32" t="n">
-        <v>6.65</v>
+        <v>10.27</v>
       </c>
       <c r="O32" t="n">
         <v>4.58</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>17.12</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="H33" t="n">
-        <v>145.5</v>
+        <v>147.95</v>
       </c>
       <c r="I33" t="n">
         <v>146.645253779084</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K33" t="n">
-        <v>1.19</v>
+        <v>-0.48</v>
       </c>
       <c r="L33" t="n">
         <v>8.15</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>7.97</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H34" t="n">
-        <v>147.5</v>
+        <v>142.8</v>
       </c>
       <c r="I34" t="n">
         <v>144.5613512317529</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.3</v>
+        <v>-3.48</v>
       </c>
       <c r="L34" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="M34" t="n">
         <v>1.84</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>13.18</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45430</v>
+        <v>45433</v>
       </c>
       <c r="H35" t="n">
-        <v>158.35</v>
+        <v>160.45</v>
       </c>
       <c r="I35" t="n">
         <v>159.2850413641436</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K35" t="n">
-        <v>-10.89</v>
+        <v>-12.36</v>
       </c>
       <c r="L35" t="n">
-        <v>11.31</v>
+        <v>16.53</v>
       </c>
       <c r="M35" t="n">
         <v>1.37</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H36" t="n">
-        <v>157.8</v>
+        <v>145.15</v>
       </c>
       <c r="I36" t="n">
         <v>146.0711678766584</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.65</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>5.05</v>
+        <v>16.39</v>
       </c>
       <c r="M36" t="n">
         <v>0.32</v>
       </c>
       <c r="N36" t="n">
-        <v>3.71</v>
+        <v>8.02</v>
       </c>
       <c r="O36" t="n">
         <v>1.33</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.27</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45453</v>
+        <v>45454</v>
       </c>
       <c r="H37" t="n">
-        <v>165.43</v>
+        <v>168.68</v>
       </c>
       <c r="I37" t="n">
         <v>167.3131084313191</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>-13.97</v>
+        <v>-16.21</v>
       </c>
       <c r="L37" t="n">
-        <v>15.4</v>
+        <v>18.36</v>
       </c>
       <c r="M37" t="n">
         <v>3.09</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.08</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45558</v>
+        <v>45559</v>
       </c>
       <c r="H38" t="n">
-        <v>239.37</v>
+        <v>211.61</v>
       </c>
       <c r="I38" t="n">
         <v>215.1397384431583</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K38" t="n">
-        <v>41.91</v>
+        <v>25.45</v>
       </c>
       <c r="L38" t="n">
         <v>5.53</v>
@@ -2607,7 +3062,7 @@
         <v>2.33</v>
       </c>
       <c r="N38" t="n">
-        <v>3.96</v>
+        <v>11.6</v>
       </c>
       <c r="O38" t="n">
         <v>1.96</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>20.91</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="H39" t="n">
-        <v>174.9</v>
+        <v>176.19</v>
       </c>
       <c r="I39" t="n">
         <v>175.6510242504007</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K39" t="n">
-        <v>17.35</v>
+        <v>16.74</v>
       </c>
       <c r="L39" t="n">
         <v>15.5</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>8.32</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H40" t="n">
-        <v>177.02</v>
+        <v>173.63</v>
       </c>
       <c r="I40" t="n">
         <v>174.9745215474313</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K40" t="n">
-        <v>0.47</v>
+        <v>-1.45</v>
       </c>
       <c r="L40" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="M40" t="n">
         <v>2.81</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.68</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="H41" t="n">
-        <v>179.67</v>
+        <v>182.83</v>
       </c>
       <c r="I41" t="n">
         <v>180.7139034734532</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.48</v>
+        <v>-5.3</v>
       </c>
       <c r="L41" t="n">
-        <v>4.56</v>
+        <v>5.83</v>
       </c>
       <c r="M41" t="n">
         <v>2.71</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>10.93</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H42" t="n">
-        <v>169.6</v>
+        <v>163.93</v>
       </c>
       <c r="I42" t="n">
         <v>164.010170867168</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.24</v>
+        <v>-10.34</v>
       </c>
       <c r="L42" t="n">
-        <v>9.09</v>
+        <v>11.43</v>
       </c>
       <c r="M42" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>3.06</v>
+        <v>3.34</v>
       </c>
       <c r="O42" t="n">
         <v>1.76</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>13.62</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H43" t="n">
-        <v>172.67</v>
+        <v>178.07</v>
       </c>
       <c r="I43" t="n">
         <v>173.0597779072009</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.33</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>5.51</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M43" t="n">
         <v>2.37</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.97</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45819</v>
+        <v>45820</v>
       </c>
       <c r="H44" t="n">
-        <v>193.68</v>
+        <v>190.21</v>
       </c>
       <c r="I44" t="n">
         <v>191.482478130437</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K44" t="n">
-        <v>8.77</v>
+        <v>6.82</v>
       </c>
       <c r="L44" t="n">
         <v>9.779999999999999</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>13.9</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="H45" t="n">
-        <v>200.99</v>
+        <v>207.96</v>
       </c>
       <c r="I45" t="n">
         <v>201.2750574398543</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.67</v>
+        <v>-9.33</v>
       </c>
       <c r="L45" t="n">
-        <v>6.46</v>
+        <v>11.32</v>
       </c>
       <c r="M45" t="n">
         <v>1.05</v>
       </c>
       <c r="N45" t="n">
-        <v>2.84</v>
+        <v>3.47</v>
       </c>
       <c r="O45" t="n">
         <v>-1.79</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.66</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H46" t="n">
-        <v>195.99</v>
+        <v>192.56</v>
       </c>
       <c r="I46" t="n">
         <v>193.9429324322393</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.76</v>
+        <v>-7.41</v>
       </c>
       <c r="L46" t="n">
-        <v>6.15</v>
+        <v>7.9</v>
       </c>
       <c r="M46" t="n">
         <v>0.5600000000000001</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.35</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H47" t="n">
-        <v>139.14</v>
+        <v>144.52</v>
       </c>
       <c r="I47" t="n">
         <v>142.8308881361914</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K47" t="n">
-        <v>27.74</v>
+        <v>24.95</v>
       </c>
       <c r="L47" t="n">
         <v>3.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H48" t="n">
-        <v>140.01</v>
+        <v>137.66</v>
       </c>
       <c r="I48" t="n">
         <v>137.6675869557129</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.12</v>
+        <v>-4.75</v>
       </c>
       <c r="L48" t="n">
-        <v>4.55</v>
+        <v>5.02</v>
       </c>
       <c r="M48" t="n">
         <v>0.35</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>10.9</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="H49" t="n">
-        <v>139.29</v>
+        <v>146.7</v>
       </c>
       <c r="I49" t="n">
         <v>145.1425311024662</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.18</v>
+        <v>-6.57</v>
       </c>
       <c r="L49" t="n">
-        <v>5.47</v>
+        <v>7.33</v>
       </c>
       <c r="M49" t="n">
         <v>0.71</v>
       </c>
       <c r="N49" t="n">
-        <v>4.39</v>
+        <v>5.32</v>
       </c>
       <c r="O49" t="n">
         <v>-1.68</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="H50" t="n">
-        <v>139.14</v>
+        <v>135.36</v>
       </c>
       <c r="I50" t="n">
         <v>137.3542438383098</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.15</v>
+        <v>-7.73</v>
       </c>
       <c r="L50" t="n">
-        <v>6.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>0.64</v>
+        <v>1.18</v>
       </c>
       <c r="N50" t="n">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="O50" t="n">
         <v>5.32</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.97</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H51" t="n">
-        <v>134.38</v>
+        <v>148.67</v>
       </c>
       <c r="I51" t="n">
         <v>142.6686829153595</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K51" t="n">
-        <v>0.72</v>
+        <v>-9.83</v>
       </c>
       <c r="L51" t="n">
-        <v>1.58</v>
+        <v>13.35</v>
       </c>
       <c r="M51" t="n">
-        <v>0.49</v>
+        <v>0.83</v>
       </c>
       <c r="N51" t="n">
-        <v>1.67</v>
+        <v>10.63</v>
       </c>
       <c r="O51" t="n">
         <v>-2.72</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>13.12</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H52" t="n">
-        <v>137</v>
+        <v>130.29</v>
       </c>
       <c r="I52" t="n">
         <v>135.2202631070006</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.85</v>
+        <v>-12.36</v>
       </c>
       <c r="L52" t="n">
-        <v>10.37</v>
+        <v>12.74</v>
       </c>
       <c r="M52" t="n">
         <v>1.82</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>17.13</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H53" t="n">
-        <v>126.97</v>
+        <v>129.44</v>
       </c>
       <c r="I53" t="n">
         <v>128.9704053287088</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K53" t="n">
-        <v>2.55</v>
+        <v>0.65</v>
       </c>
       <c r="L53" t="n">
         <v>5.14</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>10.24</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H54" t="n">
-        <v>126.92</v>
+        <v>123.23</v>
       </c>
       <c r="I54" t="n">
         <v>124.1415425517387</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.95</v>
+        <v>-4.8</v>
       </c>
       <c r="L54" t="n">
-        <v>4.05</v>
+        <v>5.49</v>
       </c>
       <c r="M54" t="n">
         <v>2.15</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.89</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="H55" t="n">
-        <v>122.8</v>
+        <v>125.7</v>
       </c>
       <c r="I55" t="n">
         <v>125.2044775333919</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K55" t="n">
-        <v>0.35</v>
+        <v>-2</v>
       </c>
       <c r="L55" t="n">
         <v>11.45</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.02</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="H56" t="n">
-        <v>122</v>
+        <v>121.8</v>
       </c>
       <c r="I56" t="n">
         <v>121.8042798783067</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.94</v>
+        <v>-3.1</v>
       </c>
       <c r="L56" t="n">
         <v>4.14</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3693,6 +4376,14 @@
       <c r="Q57" t="n">
         <v>41</v>
       </c>
+      <c r="R57" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7529,7 +8220,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="6">
@@ -7539,7 +8230,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -7549,7 +8240,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8">
@@ -7559,7 +8250,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -7569,7 +8260,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -7579,7 +8270,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105.8</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="11">
@@ -7589,7 +8280,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -7599,7 +8290,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -7609,7 +8300,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="14">
@@ -7619,7 +8310,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.54</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="15">
@@ -7629,7 +8320,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.78</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="16">
@@ -7639,7 +8330,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.18</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="17">
@@ -7649,7 +8340,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94.62</v>
+        <v>77.93000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -7659,7 +8350,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.5</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="19">
@@ -7669,7 +8360,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.67</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -7679,7 +8370,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.24</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="21">
@@ -7689,7 +8380,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.02</v>
+        <v>30.39</v>
       </c>
     </row>
     <row r="22">
@@ -7699,7 +8390,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -7709,7 +8400,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -7719,7 +8410,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="25">
@@ -7739,7 +8430,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.97</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="27">
@@ -7749,7 +8440,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.25</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="28">
@@ -7759,7 +8450,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
